--- a/MinMax/scripts/training/sweep_weights.xlsx
+++ b/MinMax/scripts/training/sweep_weights.xlsx
@@ -8,14 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu-22.04\home\bagir\Documents\1) Projects\2) AC verification\MinMax\scripts\training\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FADD674-2F56-4E1A-8F47-194242CD08A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8471991-B3A9-424B-A782-2641E89D00AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="2" xr2:uid="{87408C4C-5027-408C-9342-73FE58052C5B}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="3" xr2:uid="{87408C4C-5027-408C-9342-73FE58052C5B}"/>
   </bookViews>
   <sheets>
     <sheet name="118" sheetId="1" r:id="rId1"/>
     <sheet name="14" sheetId="3" r:id="rId2"/>
     <sheet name="57" sheetId="2" r:id="rId3"/>
+    <sheet name="300" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="12">
   <si>
     <t>pg_viol_weight</t>
   </si>
@@ -802,4 +803,169 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6EC8C5BA-3F43-4B36-939B-5A0C9D729BE3}">
+  <dimension ref="A1:E9"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="13.453125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.26953125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.54296875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="B1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="2">
+        <v>579.09773188097097</v>
+      </c>
+      <c r="C2" s="2">
+        <v>402.04483746041399</v>
+      </c>
+      <c r="D2" s="2">
+        <v>5.8435458086979404</v>
+      </c>
+      <c r="E2" s="2">
+        <v>21.460644778574601</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="2">
+        <v>7.5492644944837197</v>
+      </c>
+      <c r="C3" s="2">
+        <v>927.46350715038295</v>
+      </c>
+      <c r="D3" s="2">
+        <v>10.0556253266403</v>
+      </c>
+      <c r="E3" s="2">
+        <v>34.087407932617502</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4">
+        <v>0</v>
+      </c>
+      <c r="C4">
+        <v>0</v>
+      </c>
+      <c r="D4" s="2">
+        <v>183.62832307796299</v>
+      </c>
+      <c r="E4" s="2">
+        <v>296.54610755252401</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5">
+        <v>0</v>
+      </c>
+      <c r="C5">
+        <v>0</v>
+      </c>
+      <c r="D5" s="2">
+        <v>388.77201036051298</v>
+      </c>
+      <c r="E5" s="2">
+        <v>452.30331009048001</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>2</v>
+      </c>
+      <c r="B6" s="2">
+        <v>478.551631185031</v>
+      </c>
+      <c r="C6" s="2">
+        <v>4.1577971440272004</v>
+      </c>
+      <c r="D6">
+        <v>0</v>
+      </c>
+      <c r="E6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7" s="2">
+        <v>133.547450707108</v>
+      </c>
+      <c r="C7" s="2">
+        <v>525.74794761717703</v>
+      </c>
+      <c r="D7">
+        <v>0</v>
+      </c>
+      <c r="E7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8">
+        <v>0</v>
+      </c>
+      <c r="C8">
+        <v>0</v>
+      </c>
+      <c r="D8" s="2">
+        <v>36.3964691495149</v>
+      </c>
+      <c r="E8" s="2">
+        <v>1.6478420292198299</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>4</v>
+      </c>
+      <c r="B9" s="2">
+        <v>2.8967013457360302</v>
+      </c>
+      <c r="C9" s="2">
+        <v>1.3316530135712701</v>
+      </c>
+      <c r="D9" s="2">
+        <v>2.26418633684905</v>
+      </c>
+      <c r="E9" s="2">
+        <v>10.4167535250026</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/MinMax/scripts/training/sweep_weights.xlsx
+++ b/MinMax/scripts/training/sweep_weights.xlsx
@@ -1,22 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu-22.04\home\bagir\Documents\1) Projects\2) AC verification\MinMax\scripts\training\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8471991-B3A9-424B-A782-2641E89D00AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1EE6B3B6-CDE2-43B9-ADBF-7EA5AC715D09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="3" xr2:uid="{87408C4C-5027-408C-9342-73FE58052C5B}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{87408C4C-5027-408C-9342-73FE58052C5B}"/>
   </bookViews>
   <sheets>
     <sheet name="118" sheetId="1" r:id="rId1"/>
     <sheet name="14" sheetId="3" r:id="rId2"/>
     <sheet name="57" sheetId="2" r:id="rId3"/>
     <sheet name="300" sheetId="4" r:id="rId4"/>
+    <sheet name="793" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="12">
   <si>
     <t>pg_viol_weight</t>
   </si>
@@ -968,4 +969,171 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{969948B4-7F3F-4D5C-BFF8-BFB3CCCCF93A}">
+  <dimension ref="A1:E9"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="13.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.08984375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.26953125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.54296875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.7265625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="B1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="2">
+        <v>3.7944244335261201</v>
+      </c>
+      <c r="C2" s="2">
+        <v>4.6410230933743</v>
+      </c>
+      <c r="D2" s="2">
+        <v>186.49708500701499</v>
+      </c>
+      <c r="E2" s="2">
+        <v>8.2140627380779705</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="2">
+        <v>164.54817281642801</v>
+      </c>
+      <c r="C3" s="2">
+        <v>256.15006505026298</v>
+      </c>
+      <c r="D3" s="2">
+        <v>27.971649686369201</v>
+      </c>
+      <c r="E3" s="2">
+        <v>70.020650661104497</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4">
+        <v>0</v>
+      </c>
+      <c r="C4">
+        <v>0</v>
+      </c>
+      <c r="D4" s="2">
+        <v>50.923839432466998</v>
+      </c>
+      <c r="E4" s="2">
+        <v>42.889307454634903</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5">
+        <v>0</v>
+      </c>
+      <c r="C5">
+        <v>0</v>
+      </c>
+      <c r="D5" s="2">
+        <v>163.77118578530499</v>
+      </c>
+      <c r="E5" s="2">
+        <v>205.149286069504</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>2</v>
+      </c>
+      <c r="B6" s="2">
+        <v>38.121801604618398</v>
+      </c>
+      <c r="C6" s="2">
+        <v>78.908983777271999</v>
+      </c>
+      <c r="D6">
+        <v>0</v>
+      </c>
+      <c r="E6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7" s="2">
+        <v>17.9125293780662</v>
+      </c>
+      <c r="C7" s="2">
+        <v>974.85953195867501</v>
+      </c>
+      <c r="D7">
+        <v>0</v>
+      </c>
+      <c r="E7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8">
+        <v>0</v>
+      </c>
+      <c r="C8">
+        <v>0</v>
+      </c>
+      <c r="D8" s="2">
+        <v>42.871851376588403</v>
+      </c>
+      <c r="E8" s="2">
+        <v>6.8356105074376003</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>4</v>
+      </c>
+      <c r="B9" s="2">
+        <v>672.67755908557604</v>
+      </c>
+      <c r="C9" s="2">
+        <v>4.4208748351665497</v>
+      </c>
+      <c r="D9" s="2">
+        <v>168.29674864936601</v>
+      </c>
+      <c r="E9" s="2">
+        <v>3.1940881801540502</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>